--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935307</v>
+        <v>119935663</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,47 +1960,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585494</v>
+        <v>585356</v>
       </c>
       <c r="R13" t="n">
-        <v>7059597</v>
+        <v>7059551</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,19 +2048,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119935663</v>
+        <v>119932693</v>
       </c>
       <c r="B14" t="n">
         <v>79607</v>
@@ -2105,14 +2096,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585356</v>
+        <v>585261</v>
       </c>
       <c r="R14" t="n">
-        <v>7059551</v>
+        <v>7058971</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119932693</v>
+        <v>119935307</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,38 +2184,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585261</v>
+        <v>585494</v>
       </c>
       <c r="R15" t="n">
-        <v>7058971</v>
+        <v>7059597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935826</v>
+        <v>119935496</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,38 +2305,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585290</v>
+        <v>585495</v>
       </c>
       <c r="R16" t="n">
-        <v>7059407</v>
+        <v>7059530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935496</v>
+        <v>119935826</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,42 +2421,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585495</v>
+        <v>585290</v>
       </c>
       <c r="R17" t="n">
-        <v>7059530</v>
+        <v>7059407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935663</v>
+        <v>119935307</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,38 +1960,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585356</v>
+        <v>585494</v>
       </c>
       <c r="R13" t="n">
-        <v>7059551</v>
+        <v>7059597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,19 +2057,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119932693</v>
+        <v>119935663</v>
       </c>
       <c r="B14" t="n">
         <v>79607</v>
@@ -2096,14 +2105,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585261</v>
+        <v>585356</v>
       </c>
       <c r="R14" t="n">
-        <v>7058971</v>
+        <v>7059551</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119935307</v>
+        <v>119932693</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,47 +2193,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585494</v>
+        <v>585261</v>
       </c>
       <c r="R15" t="n">
-        <v>7059597</v>
+        <v>7058971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,12 +2281,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934878</v>
+        <v>119934320</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,38 +2649,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585620</v>
+        <v>585674</v>
       </c>
       <c r="R19" t="n">
-        <v>7059556</v>
+        <v>7059520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,19 +2746,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119932914</v>
+        <v>119934878</v>
       </c>
       <c r="B20" t="n">
         <v>79607</v>
@@ -2785,14 +2794,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585335</v>
+        <v>585620</v>
       </c>
       <c r="R20" t="n">
-        <v>7059056</v>
+        <v>7059556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,7 +2843,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2849,22 +2858,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934320</v>
+        <v>119932914</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,47 +2882,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585674</v>
+        <v>585335</v>
       </c>
       <c r="R21" t="n">
-        <v>7059520</v>
+        <v>7059056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933716</v>
+        <v>119935663</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585589</v>
+        <v>585356</v>
       </c>
       <c r="R2" t="n">
-        <v>7059386</v>
+        <v>7059551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933515</v>
+        <v>119933330</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585416</v>
+        <v>585417</v>
       </c>
       <c r="R3" t="n">
-        <v>7059345</v>
+        <v>7059207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119936442</v>
+        <v>119933023</v>
       </c>
       <c r="B4" t="n">
         <v>79607</v>
@@ -940,14 +939,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585318</v>
+        <v>585355</v>
       </c>
       <c r="R4" t="n">
-        <v>7059106</v>
+        <v>7059067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935461</v>
+        <v>119932693</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585500</v>
+        <v>585261</v>
       </c>
       <c r="R5" t="n">
-        <v>7059526</v>
+        <v>7058971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933303</v>
+        <v>119933716</v>
       </c>
       <c r="B6" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,52 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585422</v>
+        <v>585589</v>
       </c>
       <c r="R6" t="n">
-        <v>7059206</v>
+        <v>7059386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119933330</v>
+        <v>119935803</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1294,19 +1279,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585417</v>
+        <v>585315</v>
       </c>
       <c r="R7" t="n">
-        <v>7059207</v>
+        <v>7059438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935779</v>
+        <v>119933515</v>
       </c>
       <c r="B8" t="n">
         <v>79607</v>
@@ -1415,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585319</v>
+        <v>585416</v>
       </c>
       <c r="R8" t="n">
-        <v>7059424</v>
+        <v>7059345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,19 +1460,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933596</v>
+        <v>119935779</v>
       </c>
       <c r="B9" t="n">
         <v>79607</v>
@@ -1523,14 +1508,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585539</v>
+        <v>585319</v>
       </c>
       <c r="R9" t="n">
-        <v>7059340</v>
+        <v>7059424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1572,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935839</v>
+        <v>119935420</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,35 +1596,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1648,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585311</v>
+        <v>585500</v>
       </c>
       <c r="R10" t="n">
-        <v>7059400</v>
+        <v>7059553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1689,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933967</v>
+        <v>119935503</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,45 +1713,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585695</v>
+        <v>585454</v>
       </c>
       <c r="R11" t="n">
-        <v>7059489</v>
+        <v>7059586</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,22 +1806,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933560</v>
+        <v>119935307</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,38 +1830,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585521</v>
+        <v>585494</v>
       </c>
       <c r="R12" t="n">
-        <v>7059353</v>
+        <v>7059597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,22 +1927,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935307</v>
+        <v>119934878</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,47 +1951,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585494</v>
+        <v>585620</v>
       </c>
       <c r="R13" t="n">
-        <v>7059597</v>
+        <v>7059556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,22 +2039,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119935663</v>
+        <v>119933315</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,34 +2067,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585356</v>
+        <v>585442</v>
       </c>
       <c r="R14" t="n">
-        <v>7059551</v>
+        <v>7059204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,22 +2151,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119932693</v>
+        <v>119933262</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,38 +2175,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585261</v>
+        <v>585430</v>
       </c>
       <c r="R15" t="n">
-        <v>7058971</v>
+        <v>7059193</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2252,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,7 +2279,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935496</v>
+        <v>119935839</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2328,7 +2314,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2337,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585495</v>
+        <v>585311</v>
       </c>
       <c r="R16" t="n">
-        <v>7059530</v>
+        <v>7059400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,19 +2388,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935826</v>
+        <v>119932914</v>
       </c>
       <c r="B17" t="n">
         <v>79607</v>
@@ -2445,14 +2436,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585290</v>
+        <v>585335</v>
       </c>
       <c r="R17" t="n">
-        <v>7059407</v>
+        <v>7059056</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,22 +2500,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119933262</v>
+        <v>119933596</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,42 +2524,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585430</v>
+        <v>585539</v>
       </c>
       <c r="R18" t="n">
-        <v>7059193</v>
+        <v>7059340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934320</v>
+        <v>119936116</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,47 +2636,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585674</v>
+        <v>585362</v>
       </c>
       <c r="R19" t="n">
-        <v>7059520</v>
+        <v>7059291</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,22 +2724,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934878</v>
+        <v>119934864</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2770,38 +2748,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585620</v>
+        <v>585652</v>
       </c>
       <c r="R20" t="n">
-        <v>7059556</v>
+        <v>7059555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2843,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,22 +2845,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119932914</v>
+        <v>119933967</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,38 +2869,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585335</v>
+        <v>585695</v>
       </c>
       <c r="R21" t="n">
-        <v>7059056</v>
+        <v>7059489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,22 +2961,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119935242</v>
+        <v>119935710</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,35 +2985,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3031,10 +3022,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585471</v>
+        <v>585336</v>
       </c>
       <c r="R22" t="n">
-        <v>7059611</v>
+        <v>7059540</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3076,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,19 +3082,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119936116</v>
+        <v>119935826</v>
       </c>
       <c r="B23" t="n">
         <v>79607</v>
@@ -3143,10 +3134,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585362</v>
+        <v>585290</v>
       </c>
       <c r="R23" t="n">
-        <v>7059291</v>
+        <v>7059407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3169,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,7 +3179,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3215,10 +3206,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934864</v>
+        <v>119936466</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>91128</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3231,43 +3222,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585652</v>
+        <v>585314</v>
       </c>
       <c r="R24" t="n">
-        <v>7059555</v>
+        <v>7059107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3309,7 +3291,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,22 +3306,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119933363</v>
+        <v>119934320</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3348,38 +3330,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585423</v>
+        <v>585674</v>
       </c>
       <c r="R25" t="n">
-        <v>7059207</v>
+        <v>7059520</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3411,7 +3402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3421,7 +3412,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,22 +3427,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119935420</v>
+        <v>119933560</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,39 +3455,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585500</v>
+        <v>585521</v>
       </c>
       <c r="R26" t="n">
-        <v>7059553</v>
+        <v>7059353</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3514,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3524,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119936466</v>
+        <v>119935461</v>
       </c>
       <c r="B27" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,38 +3563,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585314</v>
+        <v>585500</v>
       </c>
       <c r="R27" t="n">
-        <v>7059107</v>
+        <v>7059526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119933023</v>
+        <v>119933303</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,38 +3680,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585355</v>
+        <v>585422</v>
       </c>
       <c r="R28" t="n">
-        <v>7059067</v>
+        <v>7059206</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3767,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,22 +3782,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119935503</v>
+        <v>119936442</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,42 +3810,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585454</v>
+        <v>585318</v>
       </c>
       <c r="R29" t="n">
-        <v>7059586</v>
+        <v>7059106</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119935803</v>
+        <v>119933363</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3918,42 +3918,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585315</v>
+        <v>585423</v>
       </c>
       <c r="R30" t="n">
-        <v>7059438</v>
+        <v>7059207</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3981,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3991,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4022,7 +4018,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119935710</v>
+        <v>119935496</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -4057,12 +4053,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4071,10 +4062,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585336</v>
+        <v>585495</v>
       </c>
       <c r="R31" t="n">
-        <v>7059540</v>
+        <v>7059530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4097,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4107,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4131,22 +4122,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119933315</v>
+        <v>119935242</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,34 +4150,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585442</v>
+        <v>585471</v>
       </c>
       <c r="R32" t="n">
-        <v>7059204</v>
+        <v>7059611</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4243,12 +4243,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935663</v>
+        <v>119933330</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585356</v>
+        <v>585417</v>
       </c>
       <c r="R2" t="n">
-        <v>7059551</v>
+        <v>7059207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933330</v>
+        <v>119935663</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585417</v>
+        <v>585356</v>
       </c>
       <c r="R3" t="n">
-        <v>7059207</v>
+        <v>7059551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1939,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934878</v>
+        <v>119933315</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,34 +1955,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585620</v>
+        <v>585442</v>
       </c>
       <c r="R13" t="n">
-        <v>7059556</v>
+        <v>7059204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,22 +2039,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119933315</v>
+        <v>119934878</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,34 +2067,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585442</v>
+        <v>585620</v>
       </c>
       <c r="R14" t="n">
-        <v>7059204</v>
+        <v>7059556</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,12 +2151,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119936442</v>
+        <v>119935496</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3806,38 +3806,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585318</v>
+        <v>585495</v>
       </c>
       <c r="R29" t="n">
-        <v>7059106</v>
+        <v>7059530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3869,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3879,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,19 +3898,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933363</v>
+        <v>119936442</v>
       </c>
       <c r="B30" t="n">
         <v>79607</v>
@@ -3942,14 +3946,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585423</v>
+        <v>585318</v>
       </c>
       <c r="R30" t="n">
-        <v>7059207</v>
+        <v>7059106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3981,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3991,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4006,22 +4010,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119935496</v>
+        <v>119933363</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4030,42 +4034,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585495</v>
+        <v>585423</v>
       </c>
       <c r="R31" t="n">
-        <v>7059530</v>
+        <v>7059207</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933330</v>
+        <v>119936466</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>91128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585417</v>
+        <v>585314</v>
       </c>
       <c r="R2" t="n">
-        <v>7059207</v>
+        <v>7059107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935663</v>
+        <v>119933303</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +799,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585356</v>
+        <v>585422</v>
       </c>
       <c r="R3" t="n">
-        <v>7059551</v>
+        <v>7059206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933023</v>
+        <v>119933596</v>
       </c>
       <c r="B4" t="n">
         <v>79607</v>
@@ -943,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585355</v>
+        <v>585539</v>
       </c>
       <c r="R4" t="n">
-        <v>7059067</v>
+        <v>7059340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932693</v>
+        <v>119933515</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1051,14 +1061,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585261</v>
+        <v>585416</v>
       </c>
       <c r="R5" t="n">
-        <v>7058971</v>
+        <v>7059345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933716</v>
+        <v>119933330</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1149,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585589</v>
+        <v>585417</v>
       </c>
       <c r="R6" t="n">
-        <v>7059386</v>
+        <v>7059207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935803</v>
+        <v>119933363</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,42 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585315</v>
+        <v>585423</v>
       </c>
       <c r="R7" t="n">
-        <v>7059438</v>
+        <v>7059207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119933515</v>
+        <v>119932693</v>
       </c>
       <c r="B8" t="n">
         <v>79607</v>
@@ -1396,14 +1401,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585416</v>
+        <v>585261</v>
       </c>
       <c r="R8" t="n">
-        <v>7059345</v>
+        <v>7058971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935779</v>
+        <v>119935307</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,38 +1489,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585319</v>
+        <v>585494</v>
       </c>
       <c r="R9" t="n">
-        <v>7059424</v>
+        <v>7059597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935420</v>
+        <v>119934878</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,39 +1614,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585500</v>
+        <v>585620</v>
       </c>
       <c r="R10" t="n">
-        <v>7059553</v>
+        <v>7059556</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119935503</v>
+        <v>119933967</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,46 +1722,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585454</v>
+        <v>585695</v>
       </c>
       <c r="R11" t="n">
-        <v>7059586</v>
+        <v>7059489</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,22 +1814,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119935307</v>
+        <v>119935242</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,35 +1838,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1867,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585494</v>
+        <v>585471</v>
       </c>
       <c r="R12" t="n">
-        <v>7059597</v>
+        <v>7059611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,22 +1935,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119933315</v>
+        <v>119935503</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,37 +1963,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585442</v>
+        <v>585454</v>
       </c>
       <c r="R13" t="n">
-        <v>7059204</v>
+        <v>7059586</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934878</v>
+        <v>119933315</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,34 +2080,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585620</v>
+        <v>585442</v>
       </c>
       <c r="R14" t="n">
-        <v>7059556</v>
+        <v>7059204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,19 +2164,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119933262</v>
+        <v>119935839</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2198,19 +2211,24 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585430</v>
+        <v>585311</v>
       </c>
       <c r="R15" t="n">
-        <v>7059193</v>
+        <v>7059400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,22 +2285,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935839</v>
+        <v>119935461</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,35 +2309,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2328,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585311</v>
+        <v>585500</v>
       </c>
       <c r="R16" t="n">
-        <v>7059400</v>
+        <v>7059526</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2402,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119932914</v>
+        <v>119933262</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,38 +2426,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585335</v>
+        <v>585430</v>
       </c>
       <c r="R17" t="n">
-        <v>7059056</v>
+        <v>7059193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,22 +2518,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119933596</v>
+        <v>119935496</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,38 +2542,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585539</v>
+        <v>585495</v>
       </c>
       <c r="R18" t="n">
-        <v>7059340</v>
+        <v>7059530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2736,10 +2758,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934864</v>
+        <v>119935826</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,47 +2770,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585652</v>
+        <v>585290</v>
       </c>
       <c r="R20" t="n">
-        <v>7059555</v>
+        <v>7059407</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2843,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,22 +2858,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119933967</v>
+        <v>119933560</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,42 +2882,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585695</v>
+        <v>585521</v>
       </c>
       <c r="R21" t="n">
-        <v>7059489</v>
+        <v>7059353</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2945,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2955,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,10 +2982,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119935710</v>
+        <v>119935420</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,35 +2994,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3022,10 +3027,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585336</v>
+        <v>585500</v>
       </c>
       <c r="R22" t="n">
-        <v>7059540</v>
+        <v>7059553</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,19 +3087,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119935826</v>
+        <v>119932914</v>
       </c>
       <c r="B23" t="n">
         <v>79607</v>
@@ -3130,14 +3135,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585290</v>
+        <v>585335</v>
       </c>
       <c r="R23" t="n">
-        <v>7059407</v>
+        <v>7059056</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3179,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,22 +3199,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119936466</v>
+        <v>119933716</v>
       </c>
       <c r="B24" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3218,38 +3223,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585314</v>
+        <v>585589</v>
       </c>
       <c r="R24" t="n">
-        <v>7059107</v>
+        <v>7059386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,7 +3296,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,7 +3328,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934320</v>
+        <v>119934864</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3353,12 +3363,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585674</v>
+        <v>585652</v>
       </c>
       <c r="R25" t="n">
-        <v>7059520</v>
+        <v>7059555</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3449,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119933560</v>
+        <v>119935710</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,38 +3461,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585521</v>
+        <v>585336</v>
       </c>
       <c r="R26" t="n">
-        <v>7059353</v>
+        <v>7059540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,7 +3533,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3524,7 +3543,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,22 +3558,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119935461</v>
+        <v>119933023</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3567,39 +3586,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585500</v>
+        <v>585355</v>
       </c>
       <c r="R27" t="n">
-        <v>7059526</v>
+        <v>7059067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3631,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3655,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,22 +3670,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119933303</v>
+        <v>119935779</v>
       </c>
       <c r="B28" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,52 +3694,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585422</v>
+        <v>585319</v>
       </c>
       <c r="R28" t="n">
-        <v>7059206</v>
+        <v>7059424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,22 +3782,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119935496</v>
+        <v>119935663</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3806,42 +3806,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585495</v>
+        <v>585356</v>
       </c>
       <c r="R29" t="n">
-        <v>7059530</v>
+        <v>7059551</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3869,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3879,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3910,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119936442</v>
+        <v>119934320</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3922,38 +3918,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585318</v>
+        <v>585674</v>
       </c>
       <c r="R30" t="n">
-        <v>7059106</v>
+        <v>7059520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3990,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +4000,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4022,7 +4027,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119933363</v>
+        <v>119936442</v>
       </c>
       <c r="B31" t="n">
         <v>79607</v>
@@ -4058,14 +4063,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585423</v>
+        <v>585318</v>
       </c>
       <c r="R31" t="n">
-        <v>7059207</v>
+        <v>7059106</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,7 +4102,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4107,7 +4112,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4122,22 +4127,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119935242</v>
+        <v>119935803</v>
       </c>
       <c r="B32" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4146,35 +4151,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585471</v>
+        <v>585315</v>
       </c>
       <c r="R32" t="n">
-        <v>7059611</v>
+        <v>7059438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -3449,10 +3449,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119935710</v>
+        <v>119933023</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3461,47 +3461,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585336</v>
+        <v>585355</v>
       </c>
       <c r="R26" t="n">
-        <v>7059540</v>
+        <v>7059067</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3533,7 +3524,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3543,7 +3534,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3570,7 +3561,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119933023</v>
+        <v>119935779</v>
       </c>
       <c r="B27" t="n">
         <v>79607</v>
@@ -3606,14 +3597,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585355</v>
+        <v>585319</v>
       </c>
       <c r="R27" t="n">
-        <v>7059067</v>
+        <v>7059424</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,7 +3646,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3682,10 +3673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119935779</v>
+        <v>119935710</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3694,38 +3685,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585319</v>
+        <v>585336</v>
       </c>
       <c r="R28" t="n">
-        <v>7059424</v>
+        <v>7059540</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119936466</v>
+        <v>119935461</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585314</v>
+        <v>585500</v>
       </c>
       <c r="R2" t="n">
-        <v>7059107</v>
+        <v>7059526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933303</v>
+        <v>119935779</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585422</v>
+        <v>585319</v>
       </c>
       <c r="R3" t="n">
-        <v>7059206</v>
+        <v>7059424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933596</v>
+        <v>119935839</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585539</v>
+        <v>585311</v>
       </c>
       <c r="R4" t="n">
-        <v>7059340</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933515</v>
+        <v>119936116</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585416</v>
+        <v>585362</v>
       </c>
       <c r="R5" t="n">
-        <v>7059345</v>
+        <v>7059291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933330</v>
+        <v>119933363</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585417</v>
+        <v>585423</v>
       </c>
       <c r="R6" t="n">
         <v>7059207</v>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119933363</v>
+        <v>119935496</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1261,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585423</v>
+        <v>585495</v>
       </c>
       <c r="R7" t="n">
-        <v>7059207</v>
+        <v>7059530</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119932693</v>
+        <v>119934320</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,38 +1377,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585261</v>
+        <v>585674</v>
       </c>
       <c r="R8" t="n">
-        <v>7058971</v>
+        <v>7059520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,19 +1474,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935307</v>
+        <v>119933262</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1512,24 +1521,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585494</v>
+        <v>585430</v>
       </c>
       <c r="R9" t="n">
-        <v>7059597</v>
+        <v>7059193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1590,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934878</v>
+        <v>119933967</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,38 +1614,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585620</v>
+        <v>585695</v>
       </c>
       <c r="R10" t="n">
-        <v>7059556</v>
+        <v>7059489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933967</v>
+        <v>119933716</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,42 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585695</v>
+        <v>585589</v>
       </c>
       <c r="R11" t="n">
-        <v>7059489</v>
+        <v>7059386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119935242</v>
+        <v>119935503</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,31 +1851,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1875,13 +1880,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585471</v>
+        <v>585454</v>
       </c>
       <c r="R12" t="n">
-        <v>7059611</v>
+        <v>7059586</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,22 +1940,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935503</v>
+        <v>119933596</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,42 +1968,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585454</v>
+        <v>585539</v>
       </c>
       <c r="R13" t="n">
-        <v>7059586</v>
+        <v>7059340</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,22 +2052,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119933315</v>
+        <v>119935826</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585442</v>
+        <v>585290</v>
       </c>
       <c r="R14" t="n">
-        <v>7059204</v>
+        <v>7059407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119935839</v>
+        <v>119933560</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,47 +2188,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585311</v>
+        <v>585521</v>
       </c>
       <c r="R15" t="n">
-        <v>7059400</v>
+        <v>7059353</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,22 +2276,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935461</v>
+        <v>119936442</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,39 +2304,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585500</v>
+        <v>585318</v>
       </c>
       <c r="R16" t="n">
-        <v>7059526</v>
+        <v>7059106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,22 +2388,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119933262</v>
+        <v>119933303</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>56522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,30 +2412,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2458,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585430</v>
+        <v>585422</v>
       </c>
       <c r="R17" t="n">
-        <v>7059193</v>
+        <v>7059206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2493,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119935496</v>
+        <v>119935420</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,30 +2538,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2574,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585495</v>
+        <v>585500</v>
       </c>
       <c r="R18" t="n">
-        <v>7059530</v>
+        <v>7059553</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,7 +2643,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119936116</v>
+        <v>119933023</v>
       </c>
       <c r="B19" t="n">
         <v>79607</v>
@@ -2682,14 +2679,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585362</v>
+        <v>585355</v>
       </c>
       <c r="R19" t="n">
-        <v>7059291</v>
+        <v>7059067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,19 +2743,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119935826</v>
+        <v>119932693</v>
       </c>
       <c r="B20" t="n">
         <v>79607</v>
@@ -2794,14 +2791,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585290</v>
+        <v>585261</v>
       </c>
       <c r="R20" t="n">
-        <v>7059407</v>
+        <v>7058971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2843,7 +2840,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119933560</v>
+        <v>119933315</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2886,21 +2883,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2910,10 +2907,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585521</v>
+        <v>585442</v>
       </c>
       <c r="R21" t="n">
-        <v>7059353</v>
+        <v>7059204</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,22 +2967,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119935420</v>
+        <v>119934878</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,39 +2995,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585500</v>
+        <v>585620</v>
       </c>
       <c r="R22" t="n">
-        <v>7059553</v>
+        <v>7059556</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3211,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119933716</v>
+        <v>119933330</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3223,38 +3215,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585589</v>
+        <v>585417</v>
       </c>
       <c r="R24" t="n">
-        <v>7059386</v>
+        <v>7059207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,12 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,7 +3319,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934864</v>
+        <v>119935710</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3363,7 +3354,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3373,14 +3364,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585652</v>
+        <v>585336</v>
       </c>
       <c r="R25" t="n">
-        <v>7059555</v>
+        <v>7059540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119933023</v>
+        <v>119935803</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3461,38 +3452,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585355</v>
+        <v>585315</v>
       </c>
       <c r="R26" t="n">
-        <v>7059067</v>
+        <v>7059438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3524,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3534,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3549,22 +3544,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119935779</v>
+        <v>119935242</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,34 +3572,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585319</v>
+        <v>585471</v>
       </c>
       <c r="R27" t="n">
-        <v>7059424</v>
+        <v>7059611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,22 +3665,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119935710</v>
+        <v>119936466</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91128</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,43 +3693,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585336</v>
+        <v>585314</v>
       </c>
       <c r="R28" t="n">
-        <v>7059540</v>
+        <v>7059107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,19 +3777,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119935663</v>
+        <v>119933515</v>
       </c>
       <c r="B29" t="n">
         <v>79607</v>
@@ -3834,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585356</v>
+        <v>585416</v>
       </c>
       <c r="R29" t="n">
-        <v>7059551</v>
+        <v>7059345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3869,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3879,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3906,7 +3901,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934320</v>
+        <v>119934864</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3941,12 +3936,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3955,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585674</v>
+        <v>585652</v>
       </c>
       <c r="R30" t="n">
-        <v>7059520</v>
+        <v>7059555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3990,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4000,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4027,10 +4022,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119936442</v>
+        <v>119935307</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,38 +4034,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585318</v>
+        <v>585494</v>
       </c>
       <c r="R31" t="n">
-        <v>7059106</v>
+        <v>7059597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4102,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4139,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119935803</v>
+        <v>119935663</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4151,42 +4155,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585315</v>
+        <v>585356</v>
       </c>
       <c r="R32" t="n">
-        <v>7059438</v>
+        <v>7059551</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935839</v>
+        <v>119936116</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,47 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585311</v>
+        <v>585362</v>
       </c>
       <c r="R4" t="n">
-        <v>7059400</v>
+        <v>7059291</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1004,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119936116</v>
+        <v>119933363</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1061,14 +1052,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585423</v>
       </c>
       <c r="R5" t="n">
-        <v>7059291</v>
+        <v>7059207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933363</v>
+        <v>119935839</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1140,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585423</v>
+        <v>585311</v>
       </c>
       <c r="R6" t="n">
-        <v>7059207</v>
+        <v>7059400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,12 +1237,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119936116</v>
+        <v>119935839</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585362</v>
+        <v>585311</v>
       </c>
       <c r="R4" t="n">
-        <v>7059291</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933363</v>
+        <v>119936116</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1052,14 +1061,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585423</v>
+        <v>585362</v>
       </c>
       <c r="R5" t="n">
-        <v>7059207</v>
+        <v>7059291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935839</v>
+        <v>119933363</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,47 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585311</v>
+        <v>585423</v>
       </c>
       <c r="R6" t="n">
-        <v>7059400</v>
+        <v>7059207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,12 +1237,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933515</v>
+        <v>119934864</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,38 +3801,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585416</v>
+        <v>585652</v>
       </c>
       <c r="R29" t="n">
-        <v>7059345</v>
+        <v>7059555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3874,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,22 +3898,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934864</v>
+        <v>119933515</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,47 +3922,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585652</v>
+        <v>585416</v>
       </c>
       <c r="R30" t="n">
-        <v>7059555</v>
+        <v>7059345</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,12 +4010,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935839</v>
+        <v>119936116</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,47 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585311</v>
+        <v>585362</v>
       </c>
       <c r="R4" t="n">
-        <v>7059400</v>
+        <v>7059291</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1004,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119936116</v>
+        <v>119933363</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1061,14 +1052,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585423</v>
       </c>
       <c r="R5" t="n">
-        <v>7059291</v>
+        <v>7059207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933363</v>
+        <v>119935839</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1140,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585423</v>
+        <v>585311</v>
       </c>
       <c r="R6" t="n">
-        <v>7059207</v>
+        <v>7059400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,12 +1237,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934864</v>
+        <v>119933515</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,47 +3801,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585652</v>
+        <v>585416</v>
       </c>
       <c r="R29" t="n">
-        <v>7059555</v>
+        <v>7059345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,22 +3889,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933515</v>
+        <v>119934864</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3922,38 +3913,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585416</v>
+        <v>585652</v>
       </c>
       <c r="R30" t="n">
-        <v>7059345</v>
+        <v>7059555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,12 +4010,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934320</v>
+        <v>119933716</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,47 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585674</v>
+        <v>585589</v>
       </c>
       <c r="R8" t="n">
-        <v>7059520</v>
+        <v>7059386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933262</v>
+        <v>119935503</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,45 +1494,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585430</v>
+        <v>585454</v>
       </c>
       <c r="R9" t="n">
-        <v>7059193</v>
+        <v>7059586</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,19 +1587,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119933967</v>
+        <v>119934320</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1637,7 +1634,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585695</v>
+        <v>585674</v>
       </c>
       <c r="R10" t="n">
-        <v>7059489</v>
+        <v>7059520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1708,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933716</v>
+        <v>119933262</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1732,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585589</v>
+        <v>585430</v>
       </c>
       <c r="R11" t="n">
-        <v>7059386</v>
+        <v>7059193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119935503</v>
+        <v>119933967</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,46 +1848,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585454</v>
+        <v>585695</v>
       </c>
       <c r="R12" t="n">
-        <v>7059586</v>
+        <v>7059489</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,12 +1940,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933515</v>
+        <v>119934864</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,38 +3801,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585416</v>
+        <v>585652</v>
       </c>
       <c r="R29" t="n">
-        <v>7059345</v>
+        <v>7059555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3874,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,22 +3898,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934864</v>
+        <v>119933515</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,47 +3922,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585652</v>
+        <v>585416</v>
       </c>
       <c r="R30" t="n">
-        <v>7059555</v>
+        <v>7059345</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,12 +4010,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119933716</v>
+        <v>119934320</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,38 +1377,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585589</v>
+        <v>585674</v>
       </c>
       <c r="R8" t="n">
-        <v>7059386</v>
+        <v>7059520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1474,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935503</v>
+        <v>119933262</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,46 +1498,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585454</v>
+        <v>585430</v>
       </c>
       <c r="R9" t="n">
-        <v>7059586</v>
+        <v>7059193</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1575,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,19 +1590,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934320</v>
+        <v>119933967</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1634,12 +1637,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1648,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585674</v>
+        <v>585695</v>
       </c>
       <c r="R10" t="n">
-        <v>7059520</v>
+        <v>7059489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933262</v>
+        <v>119933716</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,42 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585430</v>
+        <v>585589</v>
       </c>
       <c r="R11" t="n">
-        <v>7059193</v>
+        <v>7059386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933967</v>
+        <v>119935503</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,45 +1847,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585695</v>
+        <v>585454</v>
       </c>
       <c r="R12" t="n">
-        <v>7059489</v>
+        <v>7059586</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,12 +1940,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934864</v>
+        <v>119933515</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,47 +3801,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585652</v>
+        <v>585416</v>
       </c>
       <c r="R29" t="n">
-        <v>7059555</v>
+        <v>7059345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,22 +3889,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933515</v>
+        <v>119934864</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3922,38 +3913,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585416</v>
+        <v>585652</v>
       </c>
       <c r="R30" t="n">
-        <v>7059345</v>
+        <v>7059555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,12 +4010,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119936116</v>
+        <v>119935839</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585362</v>
+        <v>585311</v>
       </c>
       <c r="R4" t="n">
-        <v>7059291</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933363</v>
+        <v>119936116</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1052,14 +1061,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585423</v>
+        <v>585362</v>
       </c>
       <c r="R5" t="n">
-        <v>7059207</v>
+        <v>7059291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935839</v>
+        <v>119933363</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,47 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585311</v>
+        <v>585423</v>
       </c>
       <c r="R6" t="n">
-        <v>7059400</v>
+        <v>7059207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,12 +1237,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934320</v>
+        <v>119933716</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,47 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585674</v>
+        <v>585589</v>
       </c>
       <c r="R8" t="n">
-        <v>7059520</v>
+        <v>7059386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933262</v>
+        <v>119935503</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,45 +1494,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585430</v>
+        <v>585454</v>
       </c>
       <c r="R9" t="n">
-        <v>7059193</v>
+        <v>7059586</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,19 +1587,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119933967</v>
+        <v>119934320</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1637,7 +1634,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585695</v>
+        <v>585674</v>
       </c>
       <c r="R10" t="n">
-        <v>7059489</v>
+        <v>7059520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1708,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933716</v>
+        <v>119933262</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1732,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585589</v>
+        <v>585430</v>
       </c>
       <c r="R11" t="n">
-        <v>7059386</v>
+        <v>7059193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119935503</v>
+        <v>119933967</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,46 +1848,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585454</v>
+        <v>585695</v>
       </c>
       <c r="R12" t="n">
-        <v>7059586</v>
+        <v>7059489</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,12 +1940,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933515</v>
+        <v>119934864</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,38 +3801,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585416</v>
+        <v>585652</v>
       </c>
       <c r="R29" t="n">
-        <v>7059345</v>
+        <v>7059555</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3874,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,22 +3898,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934864</v>
+        <v>119933515</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,47 +3922,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585652</v>
+        <v>585416</v>
       </c>
       <c r="R30" t="n">
-        <v>7059555</v>
+        <v>7059345</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,12 +4010,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935461</v>
+        <v>119932914</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585500</v>
+        <v>585335</v>
       </c>
       <c r="R2" t="n">
-        <v>7059526</v>
+        <v>7059056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935779</v>
+        <v>119933560</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585319</v>
+        <v>585521</v>
       </c>
       <c r="R3" t="n">
-        <v>7059424</v>
+        <v>7059353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935839</v>
+        <v>119933303</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,47 +911,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585311</v>
+        <v>585422</v>
       </c>
       <c r="R4" t="n">
-        <v>7059400</v>
+        <v>7059206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119936116</v>
+        <v>119935779</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585319</v>
       </c>
       <c r="R5" t="n">
-        <v>7059291</v>
+        <v>7059424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933363</v>
+        <v>119935461</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585423</v>
+        <v>585500</v>
       </c>
       <c r="R6" t="n">
-        <v>7059207</v>
+        <v>7059526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935496</v>
+        <v>119933596</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1266,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585495</v>
+        <v>585539</v>
       </c>
       <c r="R7" t="n">
-        <v>7059530</v>
+        <v>7059340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119933716</v>
+        <v>119935710</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,38 +1378,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585589</v>
+        <v>585336</v>
       </c>
       <c r="R8" t="n">
-        <v>7059386</v>
+        <v>7059540</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1475,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935503</v>
+        <v>119933363</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,42 +1503,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585454</v>
+        <v>585423</v>
       </c>
       <c r="R9" t="n">
-        <v>7059586</v>
+        <v>7059207</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934320</v>
+        <v>119935307</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,24 +1634,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585674</v>
+        <v>585494</v>
       </c>
       <c r="R10" t="n">
-        <v>7059520</v>
+        <v>7059597</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933262</v>
+        <v>119934878</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,42 +1732,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585430</v>
+        <v>585620</v>
       </c>
       <c r="R11" t="n">
-        <v>7059193</v>
+        <v>7059556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933967</v>
+        <v>119935663</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,42 +1844,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585695</v>
+        <v>585356</v>
       </c>
       <c r="R12" t="n">
-        <v>7059489</v>
+        <v>7059551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119933596</v>
+        <v>119935242</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,34 +1960,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585539</v>
+        <v>585471</v>
       </c>
       <c r="R13" t="n">
-        <v>7059340</v>
+        <v>7059611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119935826</v>
+        <v>119935803</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,38 +2077,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585290</v>
+        <v>585315</v>
       </c>
       <c r="R14" t="n">
-        <v>7059407</v>
+        <v>7059438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119933560</v>
+        <v>119935839</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,38 +2193,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585521</v>
+        <v>585311</v>
       </c>
       <c r="R15" t="n">
-        <v>7059353</v>
+        <v>7059400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,22 +2290,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119936442</v>
+        <v>119932693</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,14 +2338,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585318</v>
+        <v>585261</v>
       </c>
       <c r="R16" t="n">
-        <v>7059106</v>
+        <v>7058971</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2402,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119933303</v>
+        <v>119935826</v>
       </c>
       <c r="B17" t="n">
-        <v>56522</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,52 +2426,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585422</v>
+        <v>585290</v>
       </c>
       <c r="R17" t="n">
-        <v>7059206</v>
+        <v>7059407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119935420</v>
+        <v>119933716</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2560,21 +2560,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585500</v>
+        <v>585589</v>
       </c>
       <c r="R18" t="n">
-        <v>7059553</v>
+        <v>7059386</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2611,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119933023</v>
+        <v>119933315</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,21 +2659,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585355</v>
+        <v>585442</v>
       </c>
       <c r="R19" t="n">
-        <v>7059067</v>
+        <v>7059204</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119932693</v>
+        <v>119935420</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,34 +2771,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585261</v>
+        <v>585500</v>
       </c>
       <c r="R20" t="n">
-        <v>7058971</v>
+        <v>7059553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119933315</v>
+        <v>119934864</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2879,38 +2884,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585442</v>
+        <v>585652</v>
       </c>
       <c r="R21" t="n">
-        <v>7059204</v>
+        <v>7059555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2956,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +2966,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934878</v>
+        <v>119933330</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,38 +3005,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585620</v>
+        <v>585417</v>
       </c>
       <c r="R22" t="n">
-        <v>7059556</v>
+        <v>7059207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3072,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3082,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,10 +3109,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119932914</v>
+        <v>119934320</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3103,38 +3121,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585335</v>
+        <v>585674</v>
       </c>
       <c r="R23" t="n">
-        <v>7059056</v>
+        <v>7059520</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3193,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3203,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,10 +3230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119933330</v>
+        <v>119936466</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>91146</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3219,38 +3246,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585417</v>
+        <v>585314</v>
       </c>
       <c r="R24" t="n">
-        <v>7059207</v>
+        <v>7059107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,10 +3342,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119935710</v>
+        <v>119933967</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,24 +3377,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585336</v>
+        <v>585695</v>
       </c>
       <c r="R25" t="n">
-        <v>7059540</v>
+        <v>7059489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3421,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3431,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,22 +3446,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119935803</v>
+        <v>119933262</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,14 +3498,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585315</v>
+        <v>585430</v>
       </c>
       <c r="R26" t="n">
-        <v>7059438</v>
+        <v>7059193</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119935242</v>
+        <v>119933515</v>
       </c>
       <c r="B27" t="n">
-        <v>57463</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3572,43 +3590,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585471</v>
+        <v>585416</v>
       </c>
       <c r="R27" t="n">
-        <v>7059611</v>
+        <v>7059345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119936466</v>
+        <v>119935503</v>
       </c>
       <c r="B28" t="n">
-        <v>91128</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,41 +3698,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585314</v>
+        <v>585454</v>
       </c>
       <c r="R28" t="n">
-        <v>7059107</v>
+        <v>7059586</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3776,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,22 +3791,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934864</v>
+        <v>119935496</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3824,24 +3838,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585652</v>
+        <v>585495</v>
       </c>
       <c r="R29" t="n">
-        <v>7059555</v>
+        <v>7059530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,22 +3907,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933515</v>
+        <v>119933023</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3946,14 +3955,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585416</v>
+        <v>585355</v>
       </c>
       <c r="R30" t="n">
-        <v>7059345</v>
+        <v>7059067</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,22 +4019,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119935307</v>
+        <v>119936442</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4034,47 +4043,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585494</v>
+        <v>585318</v>
       </c>
       <c r="R31" t="n">
-        <v>7059597</v>
+        <v>7059106</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119935663</v>
+        <v>119936116</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585356</v>
+        <v>585362</v>
       </c>
       <c r="R32" t="n">
-        <v>7059551</v>
+        <v>7059291</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -2993,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119933330</v>
+        <v>119936466</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,38 +3009,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585417</v>
+        <v>585314</v>
       </c>
       <c r="R22" t="n">
-        <v>7059207</v>
+        <v>7059107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3072,7 +3068,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3082,7 +3078,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,7 +3105,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934320</v>
+        <v>119933330</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3144,24 +3140,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585674</v>
+        <v>585417</v>
       </c>
       <c r="R23" t="n">
-        <v>7059520</v>
+        <v>7059207</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3193,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3203,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,22 +3209,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119936466</v>
+        <v>119934320</v>
       </c>
       <c r="B24" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3246,34 +3237,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585314</v>
+        <v>585674</v>
       </c>
       <c r="R24" t="n">
-        <v>7059107</v>
+        <v>7059520</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,12 +3330,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119932914</v>
+        <v>119933363</v>
       </c>
       <c r="B2" t="n">
         <v>79623</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585335</v>
+        <v>585423</v>
       </c>
       <c r="R2" t="n">
-        <v>7059056</v>
+        <v>7059207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933560</v>
+        <v>119935663</v>
       </c>
       <c r="B3" t="n">
         <v>79623</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585521</v>
+        <v>585356</v>
       </c>
       <c r="R3" t="n">
-        <v>7059353</v>
+        <v>7059551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933303</v>
+        <v>119933560</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,52 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585422</v>
+        <v>585521</v>
       </c>
       <c r="R4" t="n">
-        <v>7059206</v>
+        <v>7059353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935779</v>
+        <v>119935839</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585319</v>
+        <v>585311</v>
       </c>
       <c r="R5" t="n">
-        <v>7059424</v>
+        <v>7059400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1254,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119933596</v>
+        <v>119935496</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1261,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585539</v>
+        <v>585495</v>
       </c>
       <c r="R7" t="n">
-        <v>7059340</v>
+        <v>7059530</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935710</v>
+        <v>119936466</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,43 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585336</v>
+        <v>585314</v>
       </c>
       <c r="R8" t="n">
-        <v>7059540</v>
+        <v>7059107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,19 +1465,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933363</v>
+        <v>119935779</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1523,14 +1513,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585423</v>
+        <v>585319</v>
       </c>
       <c r="R9" t="n">
-        <v>7059207</v>
+        <v>7059424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935307</v>
+        <v>119932914</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,47 +1601,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585494</v>
+        <v>585335</v>
       </c>
       <c r="R10" t="n">
-        <v>7059597</v>
+        <v>7059056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934878</v>
+        <v>119935307</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,38 +1713,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585620</v>
+        <v>585494</v>
       </c>
       <c r="R11" t="n">
-        <v>7059556</v>
+        <v>7059597</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119935663</v>
+        <v>119933716</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,34 +1838,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585356</v>
+        <v>585589</v>
       </c>
       <c r="R12" t="n">
-        <v>7059551</v>
+        <v>7059386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1907,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935242</v>
+        <v>119935503</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,31 +1955,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1993,13 +1984,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585471</v>
+        <v>585454</v>
       </c>
       <c r="R13" t="n">
-        <v>7059611</v>
+        <v>7059586</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2028,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,22 +2044,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119935803</v>
+        <v>119933303</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,42 +2068,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585315</v>
+        <v>585422</v>
       </c>
       <c r="R14" t="n">
-        <v>7059438</v>
+        <v>7059206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,7 +2182,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119935839</v>
+        <v>119935803</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2216,12 +2217,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2230,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585311</v>
+        <v>585315</v>
       </c>
       <c r="R15" t="n">
-        <v>7059400</v>
+        <v>7059438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,22 +2286,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119932693</v>
+        <v>119933330</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,38 +2310,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585261</v>
+        <v>585417</v>
       </c>
       <c r="R16" t="n">
-        <v>7058971</v>
+        <v>7059207</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935826</v>
+        <v>119935242</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,34 +2430,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585290</v>
+        <v>585471</v>
       </c>
       <c r="R17" t="n">
-        <v>7059407</v>
+        <v>7059611</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119933716</v>
+        <v>119935710</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,38 +2547,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585589</v>
+        <v>585336</v>
       </c>
       <c r="R18" t="n">
-        <v>7059386</v>
+        <v>7059540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,12 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,22 +2644,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119933315</v>
+        <v>119934878</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,34 +2672,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585442</v>
+        <v>585620</v>
       </c>
       <c r="R19" t="n">
-        <v>7059204</v>
+        <v>7059556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2741,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,22 +2756,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119935420</v>
+        <v>119934320</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,43 +2780,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585500</v>
+        <v>585674</v>
       </c>
       <c r="R20" t="n">
-        <v>7059553</v>
+        <v>7059520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2852,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2862,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,22 +2877,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934864</v>
+        <v>119933315</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,47 +2901,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585652</v>
+        <v>585442</v>
       </c>
       <c r="R21" t="n">
-        <v>7059555</v>
+        <v>7059204</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2966,7 +2974,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,10 +3001,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119936466</v>
+        <v>119933515</v>
       </c>
       <c r="B22" t="n">
-        <v>91146</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,25 +3013,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3033,10 +3041,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585314</v>
+        <v>585416</v>
       </c>
       <c r="R22" t="n">
-        <v>7059107</v>
+        <v>7059345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,7 +3076,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,7 +3086,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3105,10 +3113,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119933330</v>
+        <v>119936116</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,42 +3125,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585417</v>
+        <v>585362</v>
       </c>
       <c r="R23" t="n">
-        <v>7059207</v>
+        <v>7059291</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3188,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3198,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,10 +3225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934320</v>
+        <v>119936442</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3233,47 +3237,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585674</v>
+        <v>585318</v>
       </c>
       <c r="R24" t="n">
-        <v>7059520</v>
+        <v>7059106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3300,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3310,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,10 +3337,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119933967</v>
+        <v>119935826</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,42 +3349,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585695</v>
+        <v>585290</v>
       </c>
       <c r="R25" t="n">
-        <v>7059489</v>
+        <v>7059407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3421,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3431,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,7 +3449,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119933262</v>
+        <v>119934864</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3493,19 +3484,24 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585430</v>
+        <v>585652</v>
       </c>
       <c r="R26" t="n">
-        <v>7059193</v>
+        <v>7059555</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3533,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3543,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,19 +3558,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119933515</v>
+        <v>119933023</v>
       </c>
       <c r="B27" t="n">
         <v>79623</v>
@@ -3610,14 +3606,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585416</v>
+        <v>585355</v>
       </c>
       <c r="R27" t="n">
-        <v>7059345</v>
+        <v>7059067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3655,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3674,19 +3670,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119935503</v>
+        <v>119935420</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3731,13 +3727,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585454</v>
+        <v>585500</v>
       </c>
       <c r="R28" t="n">
-        <v>7059586</v>
+        <v>7059553</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3766,7 +3762,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,7 +3772,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3791,19 +3787,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119935496</v>
+        <v>119933967</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3838,19 +3834,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585495</v>
+        <v>585695</v>
       </c>
       <c r="R29" t="n">
-        <v>7059530</v>
+        <v>7059489</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3882,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933023</v>
+        <v>119933262</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,38 +3927,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585355</v>
+        <v>585430</v>
       </c>
       <c r="R30" t="n">
-        <v>7059067</v>
+        <v>7059193</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,19 +4019,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119936442</v>
+        <v>119932693</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -4067,14 +4067,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585318</v>
+        <v>585261</v>
       </c>
       <c r="R31" t="n">
-        <v>7059106</v>
+        <v>7058971</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4131,19 +4131,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119936116</v>
+        <v>119933596</v>
       </c>
       <c r="B32" t="n">
         <v>79623</v>
@@ -4179,14 +4179,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585362</v>
+        <v>585539</v>
       </c>
       <c r="R32" t="n">
-        <v>7059291</v>
+        <v>7059340</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933363</v>
+        <v>119935710</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585423</v>
+        <v>585336</v>
       </c>
       <c r="R2" t="n">
-        <v>7059207</v>
+        <v>7059540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935663</v>
+        <v>119933023</v>
       </c>
       <c r="B3" t="n">
         <v>79623</v>
@@ -823,14 +832,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585356</v>
+        <v>585355</v>
       </c>
       <c r="R3" t="n">
-        <v>7059551</v>
+        <v>7059067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933560</v>
+        <v>119933330</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +920,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585521</v>
+        <v>585417</v>
       </c>
       <c r="R4" t="n">
-        <v>7059353</v>
+        <v>7059207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935839</v>
+        <v>119935503</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1036,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585311</v>
+        <v>585454</v>
       </c>
       <c r="R5" t="n">
-        <v>7059400</v>
+        <v>7059586</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935461</v>
+        <v>119935307</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,31 +1153,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585500</v>
+        <v>585494</v>
       </c>
       <c r="R6" t="n">
-        <v>7059526</v>
+        <v>7059597</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1250,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935496</v>
+        <v>119933303</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1274,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585495</v>
+        <v>585422</v>
       </c>
       <c r="R7" t="n">
-        <v>7059530</v>
+        <v>7059206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119936466</v>
+        <v>119933262</v>
       </c>
       <c r="B8" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1404,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585314</v>
+        <v>585430</v>
       </c>
       <c r="R8" t="n">
-        <v>7059107</v>
+        <v>7059193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935779</v>
+        <v>119935461</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585319</v>
+        <v>585500</v>
       </c>
       <c r="R9" t="n">
-        <v>7059424</v>
+        <v>7059526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1609,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119932914</v>
+        <v>119935496</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,38 +1633,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585335</v>
+        <v>585495</v>
       </c>
       <c r="R10" t="n">
-        <v>7059056</v>
+        <v>7059530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1725,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119935307</v>
+        <v>119935420</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,35 +1749,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1750,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585494</v>
+        <v>585500</v>
       </c>
       <c r="R11" t="n">
-        <v>7059597</v>
+        <v>7059553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1842,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933716</v>
+        <v>119936466</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>91146</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,38 +1866,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585589</v>
+        <v>585314</v>
       </c>
       <c r="R12" t="n">
-        <v>7059386</v>
+        <v>7059107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,12 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935503</v>
+        <v>119935803</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,31 +1978,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1984,13 +2010,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585454</v>
+        <v>585315</v>
       </c>
       <c r="R13" t="n">
-        <v>7059586</v>
+        <v>7059438</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,22 +2070,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119933303</v>
+        <v>119936116</v>
       </c>
       <c r="B14" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,52 +2094,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585422</v>
+        <v>585362</v>
       </c>
       <c r="R14" t="n">
-        <v>7059206</v>
+        <v>7059291</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119935803</v>
+        <v>119933363</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,42 +2206,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585315</v>
+        <v>585423</v>
       </c>
       <c r="R15" t="n">
-        <v>7059438</v>
+        <v>7059207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119933330</v>
+        <v>119935663</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,42 +2318,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585417</v>
+        <v>585356</v>
       </c>
       <c r="R16" t="n">
-        <v>7059207</v>
+        <v>7059551</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935242</v>
+        <v>119933967</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,47 +2430,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585471</v>
+        <v>585695</v>
       </c>
       <c r="R17" t="n">
-        <v>7059611</v>
+        <v>7059489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,7 +2497,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2507,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119935710</v>
+        <v>119932914</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,47 +2546,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585336</v>
+        <v>585335</v>
       </c>
       <c r="R18" t="n">
-        <v>7059540</v>
+        <v>7059056</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2619,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,10 +2646,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934878</v>
+        <v>119934320</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2668,38 +2658,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585620</v>
+        <v>585674</v>
       </c>
       <c r="R19" t="n">
-        <v>7059556</v>
+        <v>7059520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2731,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2741,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,19 +2755,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934320</v>
+        <v>119935839</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2803,24 +2802,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585674</v>
+        <v>585311</v>
       </c>
       <c r="R20" t="n">
-        <v>7059520</v>
+        <v>7059400</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2852,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2862,7 +2861,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119933315</v>
+        <v>119932693</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2905,21 +2904,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2929,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585442</v>
+        <v>585261</v>
       </c>
       <c r="R21" t="n">
-        <v>7059204</v>
+        <v>7058971</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2963,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,7 +2973,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,19 +2988,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119933515</v>
+        <v>119934878</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -3037,14 +3036,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585416</v>
+        <v>585620</v>
       </c>
       <c r="R22" t="n">
-        <v>7059345</v>
+        <v>7059556</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,7 +3075,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3086,7 +3085,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,7 +3112,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119936116</v>
+        <v>119933515</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -3153,10 +3152,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585362</v>
+        <v>585416</v>
       </c>
       <c r="R23" t="n">
-        <v>7059291</v>
+        <v>7059345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,7 +3187,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3198,7 +3197,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,7 +3224,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119936442</v>
+        <v>119935826</v>
       </c>
       <c r="B24" t="n">
         <v>79623</v>
@@ -3265,10 +3264,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585318</v>
+        <v>585290</v>
       </c>
       <c r="R24" t="n">
-        <v>7059106</v>
+        <v>7059407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3300,7 +3299,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3310,7 +3309,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,22 +3324,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119935826</v>
+        <v>119934864</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,38 +3348,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585290</v>
+        <v>585652</v>
       </c>
       <c r="R25" t="n">
-        <v>7059407</v>
+        <v>7059555</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3420,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3430,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,22 +3445,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934864</v>
+        <v>119933560</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3461,47 +3469,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585652</v>
+        <v>585521</v>
       </c>
       <c r="R26" t="n">
-        <v>7059555</v>
+        <v>7059353</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3533,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3543,7 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3558,22 +3557,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119933023</v>
+        <v>119933716</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,34 +3585,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585355</v>
+        <v>585589</v>
       </c>
       <c r="R27" t="n">
-        <v>7059067</v>
+        <v>7059386</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,7 +3654,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,22 +3674,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119935420</v>
+        <v>119935779</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,39 +3702,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585500</v>
+        <v>585319</v>
       </c>
       <c r="R28" t="n">
-        <v>7059553</v>
+        <v>7059424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3762,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3772,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,22 +3786,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933967</v>
+        <v>119933315</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3811,42 +3810,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585695</v>
+        <v>585442</v>
       </c>
       <c r="R29" t="n">
-        <v>7059489</v>
+        <v>7059204</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,22 +3898,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933262</v>
+        <v>119936442</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,42 +3922,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585430</v>
+        <v>585318</v>
       </c>
       <c r="R30" t="n">
-        <v>7059193</v>
+        <v>7059106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3994,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,19 +4010,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119932693</v>
+        <v>119933596</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -4071,10 +4062,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585261</v>
+        <v>585539</v>
       </c>
       <c r="R31" t="n">
-        <v>7058971</v>
+        <v>7059340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4097,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4107,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4134,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119933596</v>
+        <v>119935242</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,34 +4150,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585539</v>
+        <v>585471</v>
       </c>
       <c r="R32" t="n">
-        <v>7059340</v>
+        <v>7059611</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -1388,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119933262</v>
+        <v>119935461</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,42 +1400,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585430</v>
+        <v>585500</v>
       </c>
       <c r="R8" t="n">
-        <v>7059193</v>
+        <v>7059526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935461</v>
+        <v>119933262</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,43 +1517,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585500</v>
+        <v>585430</v>
       </c>
       <c r="R9" t="n">
-        <v>7059526</v>
+        <v>7059193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119936466</v>
+        <v>119936116</v>
       </c>
       <c r="B12" t="n">
-        <v>91146</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,25 +1866,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585314</v>
+        <v>585362</v>
       </c>
       <c r="R12" t="n">
-        <v>7059107</v>
+        <v>7059291</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935803</v>
+        <v>119936466</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,38 +1982,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585315</v>
+        <v>585314</v>
       </c>
       <c r="R13" t="n">
-        <v>7059438</v>
+        <v>7059107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119936116</v>
+        <v>119935803</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,38 +2090,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585362</v>
+        <v>585315</v>
       </c>
       <c r="R14" t="n">
-        <v>7059291</v>
+        <v>7059438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3336,10 +3336,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934864</v>
+        <v>119933560</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3348,47 +3348,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585652</v>
+        <v>585521</v>
       </c>
       <c r="R25" t="n">
-        <v>7059555</v>
+        <v>7059353</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3420,7 +3411,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3430,7 +3421,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3445,22 +3436,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119933560</v>
+        <v>119933716</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3473,34 +3464,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585521</v>
+        <v>585589</v>
       </c>
       <c r="R26" t="n">
-        <v>7059353</v>
+        <v>7059386</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,7 +3523,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3533,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119933716</v>
+        <v>119934864</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,38 +3577,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585589</v>
+        <v>585652</v>
       </c>
       <c r="R27" t="n">
-        <v>7059386</v>
+        <v>7059555</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,12 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3674,22 +3674,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119935779</v>
+        <v>119933315</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3702,34 +3702,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585319</v>
+        <v>585442</v>
       </c>
       <c r="R28" t="n">
-        <v>7059424</v>
+        <v>7059204</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933315</v>
+        <v>119935779</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585442</v>
+        <v>585319</v>
       </c>
       <c r="R29" t="n">
-        <v>7059204</v>
+        <v>7059424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935710</v>
+        <v>119935242</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585336</v>
+        <v>585471</v>
       </c>
       <c r="R2" t="n">
-        <v>7059540</v>
+        <v>7059611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933023</v>
+        <v>119934320</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585355</v>
+        <v>585674</v>
       </c>
       <c r="R3" t="n">
-        <v>7059067</v>
+        <v>7059520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933330</v>
+        <v>119935839</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -943,19 +952,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585417</v>
+        <v>585311</v>
       </c>
       <c r="R4" t="n">
-        <v>7059207</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,22 +1026,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119935503</v>
+        <v>119936116</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,42 +1054,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585454</v>
+        <v>585362</v>
       </c>
       <c r="R5" t="n">
-        <v>7059586</v>
+        <v>7059291</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,19 +1138,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935307</v>
+        <v>119933262</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1176,24 +1185,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585494</v>
+        <v>585430</v>
       </c>
       <c r="R6" t="n">
-        <v>7059597</v>
+        <v>7059193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,22 +1254,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119933303</v>
+        <v>119935307</v>
       </c>
       <c r="B7" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,52 +1278,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585422</v>
+        <v>585494</v>
       </c>
       <c r="R7" t="n">
-        <v>7059206</v>
+        <v>7059597</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,22 +1375,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935461</v>
+        <v>119932914</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585500</v>
+        <v>585335</v>
       </c>
       <c r="R8" t="n">
-        <v>7059526</v>
+        <v>7059056</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,19 +1487,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933262</v>
+        <v>119935803</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1545,14 +1539,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585430</v>
+        <v>585315</v>
       </c>
       <c r="R9" t="n">
-        <v>7059193</v>
+        <v>7059438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935496</v>
+        <v>119935663</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,42 +1627,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585495</v>
+        <v>585356</v>
       </c>
       <c r="R10" t="n">
-        <v>7059530</v>
+        <v>7059551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119935420</v>
+        <v>119934864</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,43 +1739,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585500</v>
+        <v>585652</v>
       </c>
       <c r="R11" t="n">
-        <v>7059553</v>
+        <v>7059555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1821,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,22 +1836,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119936116</v>
+        <v>119933330</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,38 +1860,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585362</v>
+        <v>585417</v>
       </c>
       <c r="R12" t="n">
-        <v>7059291</v>
+        <v>7059207</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119936466</v>
+        <v>119933596</v>
       </c>
       <c r="B13" t="n">
-        <v>91146</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,38 +1976,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585314</v>
+        <v>585539</v>
       </c>
       <c r="R13" t="n">
-        <v>7059107</v>
+        <v>7059340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2039,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2049,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119935803</v>
+        <v>119933363</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,42 +2088,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585315</v>
+        <v>585423</v>
       </c>
       <c r="R14" t="n">
-        <v>7059438</v>
+        <v>7059207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,7 +2188,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119933363</v>
+        <v>119934878</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2230,14 +2224,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585423</v>
+        <v>585620</v>
       </c>
       <c r="R15" t="n">
-        <v>7059207</v>
+        <v>7059556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,7 +2300,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935663</v>
+        <v>119936442</v>
       </c>
       <c r="B16" t="n">
         <v>79623</v>
@@ -2346,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585356</v>
+        <v>585318</v>
       </c>
       <c r="R16" t="n">
-        <v>7059551</v>
+        <v>7059106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2385,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,22 +2400,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119933967</v>
+        <v>119935461</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,42 +2424,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585695</v>
+        <v>585500</v>
       </c>
       <c r="R17" t="n">
-        <v>7059489</v>
+        <v>7059526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,7 +2492,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2507,7 +2502,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2534,7 +2529,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119932914</v>
+        <v>119933023</v>
       </c>
       <c r="B18" t="n">
         <v>79623</v>
@@ -2574,10 +2569,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585335</v>
+        <v>585355</v>
       </c>
       <c r="R18" t="n">
-        <v>7059056</v>
+        <v>7059067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2604,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2614,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934320</v>
+        <v>119932693</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,47 +2653,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585674</v>
+        <v>585261</v>
       </c>
       <c r="R19" t="n">
-        <v>7059520</v>
+        <v>7058971</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119935839</v>
+        <v>119935503</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2779,35 +2765,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2816,13 +2798,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585311</v>
+        <v>585454</v>
       </c>
       <c r="R20" t="n">
-        <v>7059400</v>
+        <v>7059586</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2851,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,7 +2843,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,7 +2870,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119932693</v>
+        <v>119935826</v>
       </c>
       <c r="B21" t="n">
         <v>79623</v>
@@ -2924,14 +2906,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585261</v>
+        <v>585290</v>
       </c>
       <c r="R21" t="n">
-        <v>7058971</v>
+        <v>7059407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2945,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2973,7 +2955,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,10 +2982,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934878</v>
+        <v>119933315</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3016,34 +2998,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585620</v>
+        <v>585442</v>
       </c>
       <c r="R22" t="n">
-        <v>7059556</v>
+        <v>7059204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3075,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3085,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,22 +3082,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119933515</v>
+        <v>119933716</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3128,34 +3110,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585416</v>
+        <v>585589</v>
       </c>
       <c r="R23" t="n">
-        <v>7059345</v>
+        <v>7059386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3187,7 +3169,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3197,7 +3179,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119935826</v>
+        <v>119936466</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>91146</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3236,25 +3223,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3264,10 +3251,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585290</v>
+        <v>585314</v>
       </c>
       <c r="R24" t="n">
-        <v>7059407</v>
+        <v>7059107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3309,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3448,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119933716</v>
+        <v>119935710</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,38 +3447,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585589</v>
+        <v>585336</v>
       </c>
       <c r="R26" t="n">
-        <v>7059386</v>
+        <v>7059540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3523,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3533,12 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,22 +3544,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934864</v>
+        <v>119935779</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,47 +3568,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585652</v>
+        <v>585319</v>
       </c>
       <c r="R27" t="n">
-        <v>7059555</v>
+        <v>7059424</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119933315</v>
+        <v>119933303</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,38 +3680,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585442</v>
+        <v>585422</v>
       </c>
       <c r="R28" t="n">
-        <v>7059204</v>
+        <v>7059206</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,22 +3782,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119935779</v>
+        <v>119933967</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,38 +3806,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585319</v>
+        <v>585695</v>
       </c>
       <c r="R29" t="n">
-        <v>7059424</v>
+        <v>7059489</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,22 +3898,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119936442</v>
+        <v>119935496</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3922,38 +3922,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585318</v>
+        <v>585495</v>
       </c>
       <c r="R30" t="n">
-        <v>7059106</v>
+        <v>7059530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3999,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,22 +4014,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119933596</v>
+        <v>119935420</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4038,34 +4042,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585539</v>
+        <v>585500</v>
       </c>
       <c r="R31" t="n">
-        <v>7059340</v>
+        <v>7059553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4107,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4134,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119935242</v>
+        <v>119933515</v>
       </c>
       <c r="B32" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4150,43 +4159,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585471</v>
+        <v>585416</v>
       </c>
       <c r="R32" t="n">
-        <v>7059611</v>
+        <v>7059345</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935242</v>
+        <v>119936116</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585471</v>
+        <v>585362</v>
       </c>
       <c r="R2" t="n">
-        <v>7059611</v>
+        <v>7059291</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934320</v>
+        <v>119934878</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585674</v>
+        <v>585620</v>
       </c>
       <c r="R3" t="n">
-        <v>7059520</v>
+        <v>7059556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935839</v>
+        <v>119935420</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,35 +911,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585311</v>
+        <v>585500</v>
       </c>
       <c r="R4" t="n">
-        <v>7059400</v>
+        <v>7059553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,19 +1004,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119936116</v>
+        <v>119936442</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1078,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585318</v>
       </c>
       <c r="R5" t="n">
-        <v>7059291</v>
+        <v>7059106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,19 +1116,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119933262</v>
+        <v>119935803</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1190,14 +1168,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585430</v>
+        <v>585315</v>
       </c>
       <c r="R6" t="n">
-        <v>7059193</v>
+        <v>7059438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935307</v>
+        <v>119933023</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,47 +1256,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585494</v>
+        <v>585355</v>
       </c>
       <c r="R7" t="n">
-        <v>7059597</v>
+        <v>7059067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119932914</v>
+        <v>119935779</v>
       </c>
       <c r="B8" t="n">
         <v>79623</v>
@@ -1423,14 +1392,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585335</v>
+        <v>585319</v>
       </c>
       <c r="R8" t="n">
-        <v>7059056</v>
+        <v>7059424</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119935803</v>
+        <v>119933515</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,42 +1480,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585315</v>
+        <v>585416</v>
       </c>
       <c r="R9" t="n">
-        <v>7059438</v>
+        <v>7059345</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935663</v>
+        <v>119935242</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,34 +1596,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585356</v>
+        <v>585471</v>
       </c>
       <c r="R10" t="n">
-        <v>7059551</v>
+        <v>7059611</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934864</v>
+        <v>119935663</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,47 +1713,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585652</v>
+        <v>585356</v>
       </c>
       <c r="R11" t="n">
-        <v>7059555</v>
+        <v>7059551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933330</v>
+        <v>119932914</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,42 +1825,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585417</v>
+        <v>585335</v>
       </c>
       <c r="R12" t="n">
-        <v>7059207</v>
+        <v>7059056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,12 +1913,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2076,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119933363</v>
+        <v>119933315</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2116,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585423</v>
+        <v>585442</v>
       </c>
       <c r="R14" t="n">
-        <v>7059207</v>
+        <v>7059204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2122,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,22 +2137,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934878</v>
+        <v>119935503</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,37 +2165,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585620</v>
+        <v>585454</v>
       </c>
       <c r="R15" t="n">
-        <v>7059556</v>
+        <v>7059586</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2263,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,22 +2254,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119936442</v>
+        <v>119933262</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,38 +2278,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585318</v>
+        <v>585430</v>
       </c>
       <c r="R16" t="n">
-        <v>7059106</v>
+        <v>7059193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,7 +2345,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,7 +2355,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,22 +2370,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935461</v>
+        <v>119935710</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,31 +2394,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2457,10 +2431,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585500</v>
+        <v>585336</v>
       </c>
       <c r="R17" t="n">
-        <v>7059526</v>
+        <v>7059540</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2492,7 +2466,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2502,7 +2476,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,19 +2491,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119933023</v>
+        <v>119933560</v>
       </c>
       <c r="B18" t="n">
         <v>79623</v>
@@ -2569,10 +2543,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585355</v>
+        <v>585521</v>
       </c>
       <c r="R18" t="n">
-        <v>7059067</v>
+        <v>7059353</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2614,7 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,22 +2603,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119932693</v>
+        <v>119935461</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,34 +2631,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585261</v>
+        <v>585500</v>
       </c>
       <c r="R19" t="n">
-        <v>7058971</v>
+        <v>7059526</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2695,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2726,7 +2705,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119935503</v>
+        <v>119934864</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2765,46 +2744,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585454</v>
+        <v>585652</v>
       </c>
       <c r="R20" t="n">
-        <v>7059586</v>
+        <v>7059555</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2833,7 +2816,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2843,7 +2826,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119935826</v>
+        <v>119933716</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2886,34 +2869,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585290</v>
+        <v>585589</v>
       </c>
       <c r="R21" t="n">
-        <v>7059407</v>
+        <v>7059386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,7 +2938,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,10 +2970,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119933315</v>
+        <v>119932693</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,21 +2986,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3022,10 +3010,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585442</v>
+        <v>585261</v>
       </c>
       <c r="R22" t="n">
-        <v>7059204</v>
+        <v>7058971</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,7 +3045,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3055,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,22 +3070,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119933716</v>
+        <v>119935307</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,38 +3094,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585589</v>
+        <v>585494</v>
       </c>
       <c r="R23" t="n">
-        <v>7059386</v>
+        <v>7059597</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3179,12 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,22 +3191,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119936466</v>
+        <v>119935839</v>
       </c>
       <c r="B24" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,34 +3219,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585314</v>
+        <v>585311</v>
       </c>
       <c r="R24" t="n">
-        <v>7059107</v>
+        <v>7059400</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,22 +3312,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119933560</v>
+        <v>119935496</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,38 +3336,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585521</v>
+        <v>585495</v>
       </c>
       <c r="R25" t="n">
-        <v>7059353</v>
+        <v>7059530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119935710</v>
+        <v>119936466</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,43 +3456,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585336</v>
+        <v>585314</v>
       </c>
       <c r="R26" t="n">
-        <v>7059540</v>
+        <v>7059107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3525,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,22 +3540,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119935779</v>
+        <v>119933330</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3568,38 +3564,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585319</v>
+        <v>585417</v>
       </c>
       <c r="R27" t="n">
-        <v>7059424</v>
+        <v>7059207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,22 +3656,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119933303</v>
+        <v>119934320</v>
       </c>
       <c r="B28" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,52 +3680,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585422</v>
+        <v>585674</v>
       </c>
       <c r="R28" t="n">
-        <v>7059206</v>
+        <v>7059520</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,22 +3777,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933967</v>
+        <v>119933303</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3806,42 +3801,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585695</v>
+        <v>585422</v>
       </c>
       <c r="R29" t="n">
-        <v>7059489</v>
+        <v>7059206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3910,7 +3915,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119935496</v>
+        <v>119933967</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3945,19 +3950,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585495</v>
+        <v>585695</v>
       </c>
       <c r="R30" t="n">
-        <v>7059530</v>
+        <v>7059489</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3989,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3999,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4026,10 +4031,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119935420</v>
+        <v>119933363</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4042,39 +4047,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585500</v>
+        <v>585423</v>
       </c>
       <c r="R31" t="n">
-        <v>7059553</v>
+        <v>7059207</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,7 +4143,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119933515</v>
+        <v>119935826</v>
       </c>
       <c r="B32" t="n">
         <v>79623</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585416</v>
+        <v>585290</v>
       </c>
       <c r="R32" t="n">
-        <v>7059345</v>
+        <v>7059407</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935242</v>
+        <v>119935663</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,43 +1596,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585471</v>
+        <v>585356</v>
       </c>
       <c r="R10" t="n">
-        <v>7059611</v>
+        <v>7059551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119935663</v>
+        <v>119932914</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1737,14 +1728,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585356</v>
+        <v>585335</v>
       </c>
       <c r="R11" t="n">
-        <v>7059551</v>
+        <v>7059056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1792,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119932914</v>
+        <v>119935242</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,34 +1820,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585335</v>
+        <v>585471</v>
       </c>
       <c r="R12" t="n">
-        <v>7059056</v>
+        <v>7059611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,12 +1913,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119933315</v>
+        <v>119935503</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,37 +2053,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585442</v>
+        <v>585454</v>
       </c>
       <c r="R14" t="n">
-        <v>7059204</v>
+        <v>7059586</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2122,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,10 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119935503</v>
+        <v>119933315</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,42 +2170,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585454</v>
+        <v>585442</v>
       </c>
       <c r="R15" t="n">
-        <v>7059586</v>
+        <v>7059204</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933303</v>
+        <v>119933363</v>
       </c>
       <c r="B29" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,52 +3801,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585422</v>
+        <v>585423</v>
       </c>
       <c r="R29" t="n">
-        <v>7059206</v>
+        <v>7059207</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3915,10 +3901,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933967</v>
+        <v>119935826</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,42 +3913,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585695</v>
+        <v>585290</v>
       </c>
       <c r="R30" t="n">
-        <v>7059489</v>
+        <v>7059407</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3994,7 +3976,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +3986,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,10 +4013,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119933363</v>
+        <v>119933303</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>56532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4043,38 +4025,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585423</v>
+        <v>585422</v>
       </c>
       <c r="R31" t="n">
-        <v>7059207</v>
+        <v>7059206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4102,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4112,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4139,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119935826</v>
+        <v>119933967</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4155,38 +4151,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585290</v>
+        <v>585695</v>
       </c>
       <c r="R32" t="n">
-        <v>7059407</v>
+        <v>7059489</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119936116</v>
+        <v>119935503</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585362</v>
+        <v>585454</v>
       </c>
       <c r="R2" t="n">
-        <v>7059291</v>
+        <v>7059586</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934878</v>
+        <v>119935710</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +804,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585620</v>
+        <v>585336</v>
       </c>
       <c r="R3" t="n">
-        <v>7059556</v>
+        <v>7059540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119935420</v>
+        <v>119934878</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585500</v>
+        <v>585620</v>
       </c>
       <c r="R4" t="n">
-        <v>7059553</v>
+        <v>7059556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119936442</v>
+        <v>119932693</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1052,14 +1061,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585318</v>
+        <v>585261</v>
       </c>
       <c r="R5" t="n">
-        <v>7059106</v>
+        <v>7058971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119935803</v>
+        <v>119936116</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,42 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585315</v>
+        <v>585362</v>
       </c>
       <c r="R6" t="n">
-        <v>7059438</v>
+        <v>7059291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119933023</v>
+        <v>119935803</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,38 +1261,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585355</v>
+        <v>585315</v>
       </c>
       <c r="R7" t="n">
-        <v>7059067</v>
+        <v>7059438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1353,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935779</v>
+        <v>119935461</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585319</v>
+        <v>585500</v>
       </c>
       <c r="R8" t="n">
-        <v>7059424</v>
+        <v>7059526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,19 +1470,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933515</v>
+        <v>119933560</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1504,14 +1518,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585416</v>
+        <v>585521</v>
       </c>
       <c r="R9" t="n">
-        <v>7059345</v>
+        <v>7059353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119935663</v>
+        <v>119936466</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>91146</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1606,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585356</v>
+        <v>585314</v>
       </c>
       <c r="R10" t="n">
-        <v>7059551</v>
+        <v>7059107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119932914</v>
+        <v>119933967</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,38 +1718,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585335</v>
+        <v>585695</v>
       </c>
       <c r="R11" t="n">
-        <v>7059056</v>
+        <v>7059489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119935242</v>
+        <v>119933262</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,47 +1834,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585471</v>
+        <v>585430</v>
       </c>
       <c r="R12" t="n">
-        <v>7059611</v>
+        <v>7059193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119933596</v>
+        <v>119935839</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,38 +1950,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585539</v>
+        <v>585311</v>
       </c>
       <c r="R13" t="n">
-        <v>7059340</v>
+        <v>7059400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119935503</v>
+        <v>119933023</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,42 +2075,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585454</v>
+        <v>585355</v>
       </c>
       <c r="R14" t="n">
-        <v>7059586</v>
+        <v>7059067</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119933315</v>
+        <v>119936442</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,34 +2187,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585442</v>
+        <v>585318</v>
       </c>
       <c r="R15" t="n">
-        <v>7059204</v>
+        <v>7059106</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,7 +2283,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119933262</v>
+        <v>119935496</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2301,19 +2318,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585430</v>
+        <v>585495</v>
       </c>
       <c r="R16" t="n">
-        <v>7059193</v>
+        <v>7059530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2355,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935710</v>
+        <v>119935420</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,35 +2411,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2431,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585336</v>
+        <v>585500</v>
       </c>
       <c r="R17" t="n">
-        <v>7059540</v>
+        <v>7059553</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,22 +2504,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119933560</v>
+        <v>119933716</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,34 +2532,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585521</v>
+        <v>585589</v>
       </c>
       <c r="R18" t="n">
-        <v>7059353</v>
+        <v>7059386</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119935461</v>
+        <v>119933315</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,39 +2649,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585500</v>
+        <v>585442</v>
       </c>
       <c r="R19" t="n">
-        <v>7059526</v>
+        <v>7059204</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2705,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,19 +2733,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934864</v>
+        <v>119933330</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2767,24 +2780,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585652</v>
+        <v>585417</v>
       </c>
       <c r="R20" t="n">
-        <v>7059555</v>
+        <v>7059207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,7 +2824,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,7 +2834,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,22 +2849,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119933716</v>
+        <v>119935242</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,34 +2877,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585589</v>
+        <v>585471</v>
       </c>
       <c r="R21" t="n">
-        <v>7059386</v>
+        <v>7059611</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,7 +2945,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2938,12 +2955,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,7 +2982,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119932693</v>
+        <v>119933515</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -3006,14 +3018,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585261</v>
+        <v>585416</v>
       </c>
       <c r="R22" t="n">
-        <v>7058971</v>
+        <v>7059345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,10 +3094,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119935307</v>
+        <v>119935826</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3094,47 +3106,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585494</v>
+        <v>585290</v>
       </c>
       <c r="R23" t="n">
-        <v>7059597</v>
+        <v>7059407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3169,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3179,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,19 +3194,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119935839</v>
+        <v>119935307</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3238,7 +3241,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3252,10 +3255,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585311</v>
+        <v>585494</v>
       </c>
       <c r="R24" t="n">
-        <v>7059400</v>
+        <v>7059597</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3290,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3300,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,10 +3327,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119935496</v>
+        <v>119933363</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,42 +3339,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585495</v>
+        <v>585423</v>
       </c>
       <c r="R25" t="n">
-        <v>7059530</v>
+        <v>7059207</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3412,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119936466</v>
+        <v>119934320</v>
       </c>
       <c r="B26" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,34 +3455,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585314</v>
+        <v>585674</v>
       </c>
       <c r="R26" t="n">
-        <v>7059107</v>
+        <v>7059520</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3515,7 +3523,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3525,7 +3533,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,19 +3548,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119933330</v>
+        <v>119934864</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3587,19 +3595,24 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585417</v>
+        <v>585652</v>
       </c>
       <c r="R27" t="n">
-        <v>7059207</v>
+        <v>7059555</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3631,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,22 +3669,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934320</v>
+        <v>119933596</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,47 +3693,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585674</v>
+        <v>585539</v>
       </c>
       <c r="R28" t="n">
-        <v>7059520</v>
+        <v>7059340</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3756,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3766,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,19 +3781,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119933363</v>
+        <v>119932914</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3829,10 +3833,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585423</v>
+        <v>585335</v>
       </c>
       <c r="R29" t="n">
-        <v>7059207</v>
+        <v>7059056</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,7 +3868,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3874,7 +3878,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,22 +3893,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119935826</v>
+        <v>119933303</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>56532</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,38 +3917,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585290</v>
+        <v>585422</v>
       </c>
       <c r="R30" t="n">
-        <v>7059407</v>
+        <v>7059206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3986,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +4031,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119933303</v>
+        <v>119935779</v>
       </c>
       <c r="B31" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,52 +4043,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585422</v>
+        <v>585319</v>
       </c>
       <c r="R31" t="n">
-        <v>7059206</v>
+        <v>7059424</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4102,7 +4106,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4127,22 +4131,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119933967</v>
+        <v>119935663</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4151,42 +4155,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585695</v>
+        <v>585356</v>
       </c>
       <c r="R32" t="n">
-        <v>7059489</v>
+        <v>7059551</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119935503</v>
+        <v>119933967</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585454</v>
+        <v>585695</v>
       </c>
       <c r="R2" t="n">
-        <v>7059586</v>
+        <v>7059489</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119935710</v>
+        <v>119935242</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585336</v>
+        <v>585471</v>
       </c>
       <c r="R3" t="n">
-        <v>7059540</v>
+        <v>7059611</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +900,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934878</v>
+        <v>119933716</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585620</v>
+        <v>585589</v>
       </c>
       <c r="R4" t="n">
-        <v>7059556</v>
+        <v>7059386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932693</v>
+        <v>119935826</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1061,14 +1065,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585261</v>
+        <v>585290</v>
       </c>
       <c r="R5" t="n">
-        <v>7058971</v>
+        <v>7059407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119936116</v>
+        <v>119933303</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1153,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585362</v>
+        <v>585422</v>
       </c>
       <c r="R6" t="n">
-        <v>7059291</v>
+        <v>7059206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119935803</v>
+        <v>119932693</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1279,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585315</v>
+        <v>585261</v>
       </c>
       <c r="R7" t="n">
-        <v>7059438</v>
+        <v>7058971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119935461</v>
+        <v>119933560</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,39 +1395,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585500</v>
+        <v>585521</v>
       </c>
       <c r="R8" t="n">
-        <v>7059526</v>
+        <v>7059353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119933560</v>
+        <v>119933315</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1507,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585521</v>
+        <v>585442</v>
       </c>
       <c r="R9" t="n">
-        <v>7059353</v>
+        <v>7059204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1591,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119936466</v>
+        <v>119933363</v>
       </c>
       <c r="B10" t="n">
-        <v>91146</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,38 +1615,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585314</v>
+        <v>585423</v>
       </c>
       <c r="R10" t="n">
-        <v>7059107</v>
+        <v>7059207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119933967</v>
+        <v>119933596</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,42 +1727,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585695</v>
+        <v>585539</v>
       </c>
       <c r="R11" t="n">
-        <v>7059489</v>
+        <v>7059340</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933262</v>
+        <v>119934320</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1857,19 +1862,24 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585430</v>
+        <v>585674</v>
       </c>
       <c r="R12" t="n">
-        <v>7059193</v>
+        <v>7059520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1921,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1936,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119935839</v>
+        <v>119936116</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,47 +1960,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585311</v>
+        <v>585362</v>
       </c>
       <c r="R13" t="n">
-        <v>7059400</v>
+        <v>7059291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,19 +2048,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119933023</v>
+        <v>119933515</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -2095,14 +2096,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585355</v>
+        <v>585416</v>
       </c>
       <c r="R14" t="n">
-        <v>7059067</v>
+        <v>7059345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,19 +2160,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119936442</v>
+        <v>119935779</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2211,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585318</v>
+        <v>585319</v>
       </c>
       <c r="R15" t="n">
-        <v>7059106</v>
+        <v>7059424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119935496</v>
+        <v>119936466</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,38 +2300,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585495</v>
+        <v>585314</v>
       </c>
       <c r="R16" t="n">
-        <v>7059530</v>
+        <v>7059107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119935420</v>
+        <v>119933262</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,43 +2408,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585500</v>
+        <v>585430</v>
       </c>
       <c r="R17" t="n">
-        <v>7059553</v>
+        <v>7059193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119933716</v>
+        <v>119936442</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,34 +2528,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585589</v>
+        <v>585318</v>
       </c>
       <c r="R18" t="n">
-        <v>7059386</v>
+        <v>7059106</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119933315</v>
+        <v>119934864</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,38 +2636,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585442</v>
+        <v>585652</v>
       </c>
       <c r="R19" t="n">
-        <v>7059204</v>
+        <v>7059555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119933330</v>
+        <v>119935663</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2757,42 +2757,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585417</v>
+        <v>585356</v>
       </c>
       <c r="R20" t="n">
-        <v>7059207</v>
+        <v>7059551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2834,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119935242</v>
+        <v>119935307</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,35 +2869,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2910,10 +2906,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585471</v>
+        <v>585494</v>
       </c>
       <c r="R21" t="n">
-        <v>7059611</v>
+        <v>7059597</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119933515</v>
+        <v>119935803</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,38 +2990,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585416</v>
+        <v>585315</v>
       </c>
       <c r="R22" t="n">
-        <v>7059345</v>
+        <v>7059438</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119935826</v>
+        <v>119935461</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3110,34 +3110,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585290</v>
+        <v>585500</v>
       </c>
       <c r="R23" t="n">
-        <v>7059407</v>
+        <v>7059526</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3179,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119935307</v>
+        <v>119934878</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3218,47 +3223,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585494</v>
+        <v>585620</v>
       </c>
       <c r="R24" t="n">
-        <v>7059597</v>
+        <v>7059556</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3290,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3300,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,22 +3311,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119933363</v>
+        <v>119935839</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,38 +3335,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585423</v>
+        <v>585311</v>
       </c>
       <c r="R25" t="n">
-        <v>7059207</v>
+        <v>7059400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3427,22 +3432,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934320</v>
+        <v>119932914</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,47 +3456,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585674</v>
+        <v>585335</v>
       </c>
       <c r="R26" t="n">
-        <v>7059520</v>
+        <v>7059056</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3523,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3533,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3560,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934864</v>
+        <v>119933023</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3572,47 +3568,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget, Rågsvedjeberget, Ång</t>
+          <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585652</v>
+        <v>585355</v>
       </c>
       <c r="R27" t="n">
-        <v>7059555</v>
+        <v>7059067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119933596</v>
+        <v>119933330</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,38 +3680,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ottomyran, Ottomyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585539</v>
+        <v>585417</v>
       </c>
       <c r="R28" t="n">
-        <v>7059340</v>
+        <v>7059207</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3756,7 +3747,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3766,7 +3757,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3793,10 +3784,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119932914</v>
+        <v>119935496</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,38 +3796,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585335</v>
+        <v>585495</v>
       </c>
       <c r="R29" t="n">
-        <v>7059056</v>
+        <v>7059530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3868,7 +3863,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3878,7 +3873,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,22 +3888,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119933303</v>
+        <v>119935503</v>
       </c>
       <c r="B30" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3917,55 +3912,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottomyran, Ottomyran, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585422</v>
+        <v>585454</v>
       </c>
       <c r="R30" t="n">
-        <v>7059206</v>
+        <v>7059586</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3994,7 +3980,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +3990,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,22 +4005,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119935779</v>
+        <v>119935710</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4043,38 +4029,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585319</v>
+        <v>585336</v>
       </c>
       <c r="R31" t="n">
-        <v>7059424</v>
+        <v>7059540</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,7 +4101,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4116,7 +4111,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119935663</v>
+        <v>119935420</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,34 +4154,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585356</v>
+        <v>585500</v>
       </c>
       <c r="R32" t="n">
-        <v>7059551</v>
+        <v>7059553</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>119936466</v>
       </c>
       <c r="B16" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 36499-2024 artfynd.xlsx
+++ b/artfynd/A 36499-2024 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>119936466</v>
       </c>
       <c r="B16" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
